--- a/data/report/20260419_ranking.xlsx
+++ b/data/report/20260419_ranking.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="naver_10" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="naver_hot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="naver_down" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coupang_10" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coupang_hot" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coupang_down" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oliveyoung_10" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oliveyoung_hot" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oliveyoung_down" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kakao_10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kakao_hot" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kakao_down" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daiso_10" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daiso_hot" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daiso_down" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="naver_10" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="naver_hot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="naver_down" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="coupang_10" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="coupang_hot" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="coupang_down" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="oliveyoung_10" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="oliveyoung_hot" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="oliveyoung_down" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="kakao_10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="kakao_hot" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kakao_down" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="daiso_10" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="daiso_hot" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="daiso_down" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,16 +31,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,21 +56,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,72 +431,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -545,7 +533,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=rHv%2FQBe4xGbZD2FjePjRzP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcUBg1WD9uhJQabJJDT3sdGf8FndFmTfOYmsdPDqD3EKhZKcHa07pMq%2B8oRqlnV3%2BmqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tvTsrr596l%2FCtQiKDXWrYchILcYB2wl6oHYSLNtZAhdWi1eYscjgtdhV4FDznS96yC3PyuZLo0mcOJ3OhjK68cU%2FJcAO4BSEkL6XXJ73dVWnnb1aPKi4BHcA5asJqy4261S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/withvitamin/products/138663861</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -595,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=MOokgH4TamsPYfCc5nYT5v%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdGGy9vQmujUY74or2Gq94L71k9O8D33d%2BPuAUxCYyBkQSjD%2BLxI7anlMQEWf%2FiPRiqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tQIGEFTYSDvFct1eCXSkgemIc685hpCbhhxAARWNvxfKi1eYscjgtdhV4FDznS96yob6rVCvPNGDeljn5bJ7067tKz0%2FrSDQsUQn7g4UVfJNADd4rRZfdcjeduOJe%2B8gd1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/9669821031</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -645,7 +633,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Q7hPaJe5IZETUKWowuIXSP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtepw%2BeKlnKO%2BsHSjfV6ID%2FLRTU7ZLzlWi5zLdSqjANpby%2F6TZwgPH169XsogdZ8Fz%2BqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1ts7PT%2FXZ5iy2sL4Vw%2FlIjJjix6leAYIz5lot2QB82xEWi1eYscjgtdhV4FDznS96yLjcxZYC2rDItIlEazxLO3aIiz848hW2VWUzBMu8pwF98IEb71AXqENQmutYNSBnX1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/bnrmall/products/4755872512</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -695,7 +683,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=e1ivc2KR%2BdKcPr3liLzPT%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteJk9tO6qWixJ1glP627I62JQ11J%2FOFWAhodWCUoeaoHyFtbFUkU2tv8275dHCmjIGqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tfuuhBAexzEcFEtNDgoRgS244JkfouBuQoTC8QeHFd%2Bii1eYscjgtdhV4FDznS96ygVIYEMqiwXS48EgF3MDVxEdtIx8apT5ARHhT8Epp16Hym3hiC91uolg9cS9N1IVm1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/grainon/products/7999337429</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -745,7 +733,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=qunBibSmalpa5hAxYZ1ggv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcQNZgW7V2pSF%2BySUn6xJSivbUU24XBrAGJeguZLp9FtQ0SsyPcy1O5b1Ylbw5URreqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t%2F9BR72Sdqj03S2PPCL4o7sEoe8K826t4eD8ALjSpKjKi1eYscjgtdhV4FDznS96yzH3oCPbzvCv7iOWLUVl9rYj1wk4WRQUZUme58LuomtZ9nnPCWkcUUyLyDWvshDHZ1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/5866524379</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -795,7 +783,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=JjkeQ%2FrJS%2F3SUZFiVlfBnP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcPTcwt7GHf%2F4ztJyEaYtF7YoKs3TNTP8BO0IFC0qJj6d5AJ%2B0234M9InyjjaOTA4iqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tKFCwW%2Bvxq1OswghpASZYFP%2FO7UC3Sx1NZvjs4wSl0Wqi1eYscjgtdhV4FDznS96ydy4PwO%2FToPP%2B9vaais5yrShvs6afH5vdFzOkU27nDHkV%2FKMGZi6tBP60tGmSYu3k1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/gnm/products/12058710926</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -845,7 +833,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=eW0y5faAh4ak8Pf9g5AKA%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcy78PLPWI%2BCqyHM5CClx10wxbb%2BF6elR%2Fe69AR1JKP4fvwgIVYItLX9d0MJSf77yuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t5%2FE8JbKIUN3pp3J5STt%2BZUiy0Sq6GliW2wsGL35f372i1eYscjgtdhV4FDznS96yfoRpSL9VMi%2BpepEAlwF8qDfJiQr4WkRvxrLNmTMVWpfDsoPt6BvB3921LKbe0gXF1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/kdietcode/products/12168694379</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -895,7 +883,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Na1GzTpCWoqtjg0UpheF0v%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtchxLb5xsv01GdCPb7phF4nj%2BwuPbrgDQGsD6zbRYAT3tf0IiZboemZ0h%2BYqJlM0bqqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t2bIe1kpVwy38TAuJlenLMu0%2BOJzq62aRzTurG0P%2FNm6i1eYscjgtdhV4FDznS96y7ufNsm503LIN2wfRO60bXaVGuYp12la%2BT3jDxgbIGDl2A%2Fwe5nAJbQyblRQJxFdh1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/josunbichaek/products/4989004696</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -945,7 +933,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=AT15Bpwob0HzPq%2BQRghWVf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtct55NaqiXB9PVyRkwJNBOOV%2B6GoYrkBBsLdKN%2BWY8NTWj9Bylq4bpWdgvBBAL2fE2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tOhtnoKWIWI7Mce%2BQgHxR5rkG4JfxK8V6pTRnRnSO4Qai1eYscjgtdhV4FDznS96yIzgpEUA7sQF%2BFuOWNPtWHTLBfJg%2BU8jRlq6xAC7malm0moykVtcbfgOMPvtYP9521S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/gnm/products/5159725770</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -995,7 +983,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=SNqY%2FexVJA0Evpjl82F97f%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtchpStit7KwyHjEydGRLbhCQPN8LsS3%2FrjRfCUMQe4okq7FtW1NaKKPwajzRik2l7WqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tuEs0OnHFxP5QTW%2FnrFTMTU9UHLUoI7pJGus8LxTXDRtTx1%2Ff2GvzCMPu85yMI%2BZSvw50Fa21uPh8ScAWekisrHGBxEU3H1d9FApf0WxZBHWdSUB7ANbtoVQiqONYG4arq8BgUXkx2QwdSgeUpurqi4EIm5jsLxwOcg1z%2BeQmWeAFwWpYQz6orjPG3UcRJRrBMzvEJk5wSyFgIyn4086xI1bGBdfnM4cK08LHAfZ6Hv0%3D</t>
+          <t>https://smartstore.naver.com/gnm/products/232155349</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1029,67 +1017,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>like</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>img_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>like_diff</t>
         </is>
@@ -1600,67 +1588,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>like</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>img_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>like_diff</t>
         </is>
@@ -7659,67 +7647,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>like</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>img_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>like_diff</t>
         </is>
@@ -15090,72 +15078,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -15658,72 +15646,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -22872,72 +22860,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -33720,72 +33708,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -33822,7 +33810,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=AT15Bpwob0HzPq%2BQRghWVf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtct55NaqiXB9PVyRkwJNBOOV%2B6GoYrkBBsLdKN%2BWY8NTWj9Bylq4bpWdgvBBAL2fE2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tOhtnoKWIWI7Mce%2BQgHxR5rkG4JfxK8V6pTRnRnSO4Qai1eYscjgtdhV4FDznS96yIzgpEUA7sQF%2BFuOWNPtWHTLBfJg%2BU8jRlq6xAC7malm0moykVtcbfgOMPvtYP9521S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/gnm/products/5159725770</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -33872,7 +33860,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=KY040%2BzbluTMwm%2BFeV3RtP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfsLMFr5E41M9C%2FyildaFz8rA%2FSJEfjJPeXNskq7J8fl3VU9yveD5RJ6IVoiAu600qqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tQILq3GaniQ9uTTlC4MD4ERI8wq11ATfubopwer2ASm%2Bi1eYscjgtdhV4FDznS96yHxIA8pu8PM8MewL9zGF0ZJEkyK8kv%2FnbkPcczGMPhtEkVT%2F4owy9JYNCwCWLznHm1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/malldaewoong/products/12727841644</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -33922,7 +33910,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Rn4IOvvWd27dU6l%2FmbqA6P%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteS1ZFLbmyQazfsdhF30sRa%2FHcUyvixicyZj0GTkp3S%2BKtcdNWLqKcNTYVzrPBEFPyqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t0%2BY9ZobhpuhasCfwrfJX%2BOKnAapf9%2FUgareFtcL6qhui1eYscjgtdhV4FDznS96yy65tq4uryzbQCDhRSSU5nYCxKPCP4k%2FACYqC%2BgrvB0dd24uJR90%2BprDxgqitB2MQ1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/jyns/products/6721400779</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -33972,7 +33960,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=GrOsQwvB3mJKNYpkMTXCn%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfAuMkgbKZM9XA8uYv7DLfanyqgoWZK0VTF5W5fPVHnK%2FPtV3jjAY52SbVkCQfVs6aqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tS9a5zvcHXPiGvj1uYEVhl5WB6BBkJC%2FQj7mfRZhR13Wi1eYscjgtdhV4FDznS96yDa0akHXmJ7bBu5G13NiDU1Si%2FcHUJLJHy9xciTWH7BAH5qm3NKf%2FY1hsFZ5x7vDg1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/hiwater/products/9240775762</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -34022,7 +34010,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=D8A7JS%2Fa0fYoCtlVvVtOjv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtevuqt6kujJ3w9k5fM%2B8AedobloLDXJa8vuFUT2O99M6oJfxG%2F4RpERRxabd9bt%2BjuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tJdW5WQX7Sw%2BIgNmmAvPQzxVT0V3UztXNXYFSkTpFlMWi1eYscjgtdhV4FDznS96yc4hQzIxyvN0kyC0ShPtz5hO1ZLk3F7ZfMkLlu59BUIUGYO%2BFpTWTzQNuPjcTx6cY1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/ollocdam/products/11957648841</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -34072,7 +34060,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=ksHm7CVf%2FzSra94czbqB1f%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhte1ueEFDIJ%2BYtGgJOtA346LqNMK3w5iTocvI3FqSi0QPpScpa1pgJ0UTU12j3XsMJyqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tTlnRRyS8rqRK%2B7dceesVVqcP8LVrAo4r35ZMhcn1r6mi1eYscjgtdhV4FDznS96y4uY642rXpbJa47Direccwb1m6wXc3Hs%2B4zGxlNzNNdckrlD%2FCWQojTrfaEQ4EIl41S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/wellness-pick/products/13025500740</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -34122,7 +34110,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Vf5DDR4xgztacY0vIJ639f%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteVYEY2O7dk%2FMj6pOLd2RDP3jmwOhdHoL2bt%2FVobd70XnaQVFNKcV9Ib6rHfMUmXUmqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tBvhuAe1mYb%2BYo%2FZQ0u8eL3E%2BF6QmX31UtEM5lnTEeQii1eYscjgtdhV4FDznS96y58V1GyYZr4iH1eO34eAQosQKycsa%2BLwnnO3UZ3LKknNt4tQJP0gxKoTNlZ%2Fw7EF01S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/kgcshop2304/products/10556547785</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -34172,7 +34160,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=09bzqDd06R1mJfMWGS%2FuGv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdmuBTJjbZUEBmQLCsIZ2DwgOZQ%2BVxAuuQ7g2nd7ZFHETnTJG9W5FJUyl0ifo5c7NiqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tAL7bG7Uawh%2FagusHDyEokhSmoagK6Ut61nKZsr3jm5Wi1eYscjgtdhV4FDznS96yx0FGrWb5BumB2B4sgFBozFzLh1QbkGg%2B%2F7LRN6wpu%2BOLQymQydo3nMl6FiH%2FqwI81S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/11585234218</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -34222,7 +34210,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=tN0YrifctMqHCSSxEsHjDv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtd4mwlvJIZAscMGNEEkYwYGxyTY0pGxtqS7Ne1PPGWLRSsKgWHkGpmQ8btOlMkvulyqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tOe0nQFfQEJUlVJWpKjPeUY1yMc9%2FC18bdWsekYFTE4Wi1eYscjgtdhV4FDznS96yC3BBiVat6yYziUY4nCkDgLhPE2KMmnzWyvpTkDDmGr%2FhWB%2FLqukq8Ma6oIQM0bnV1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/cellguardian/products/11293123503</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -34272,7 +34260,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=022ai0mqkDSIlqXFRtj6hv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteiplv%2FTS2ZastwWB6fMTygdDsn7eWkuxkFpEU9kLRg8e02CBoaHszstqr8ZE9LyVWqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t9fuxNug16Y%2F%2FeiRAyhOCXGlRwhtCt22HTQF43IdO5F2i1eYscjgtdhV4FDznS96yjiliDWWWbCVsx59D1gcPsDGzU7EQlJ4ki9lHQFfrHYcSUXllw1U%2BsSh6DsAhM3qK1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/siruchoice/products/8238403743</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -34322,7 +34310,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=puK0MiC3dzvyqagaJV4cMP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtd7VOb5hRKRs%2FOU%2Bnmo8ckaz6Mw%2F7Y0VxI%2B0FHJ%2Bxs0E%2BuN4R%2BbOL783%2F7yfBv%2BDL2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tIk8cHoh5vuvYNDhu9P1RQlkBoR6CGpwWa%2FpFzKYBSfyi1eYscjgtdhV4FDznS96yyB9uph8nlPQIXoxgVLNgALmiuAYeayj14Y16wIepMrC%2FoHUXSlky6JMsvScb1qw61S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/tsshop1/products/9243303137</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -34372,7 +34360,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=br7omrX6O1dqXnCmwc%2BXgf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdAA4fUgXRpumVF6TiAmjOsa40wGMPICDFYLS%2BfeuHtKgOqYQuyPXukEQvUrif5twqqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tlZuFlEEHbVeym1bIjCuCtlWUFXBdd%2BWKyBhGboXkfWCi1eYscjgtdhV4FDznS96yc%2FngBp02OlFSkhMgXEPCHPpL4U2P1SZB7sSSf15KLN4u%2Fh2%2FVPL9sRqKMiVPH5yL1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/nutricore/products/9953260627</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -34422,7 +34410,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=4028nQz95JWpxVesthtaFf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtd2Lsasknfcje5fhQ97dBqrPfBAZS0P5UAB9gRDGDtBez9iXf2lfXKHezma7EsJkpuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tT4H%2B%2FBv7zRZ67Y2HO%2B3LsQdK%2FwvNk4JF6xK0ymQWhYii1eYscjgtdhV4FDznS96yQJb%2Bnz0LhIz%2FcIyCU2HXn4DAU9SjiyI4eSPvrK6terIkBTmkORePYMLpeKDy%2B%2B0n1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/healthnaturestore/products/12275880717</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -34472,7 +34460,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=bKxjzJNzHUu3wJtty3nMS%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtc03M0hW72SCae%2BX3qOW9ziM%2F4diSEWY3jT34RxQ05bG4omV8olbj17G3paTQ67emuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1td%2FSby1SvAb4WHpxkawXHni37sGP345kw%2BNh1f5Kzgm6i1eYscjgtdhV4FDznS96y7qq1clO4XLyvoC3DYtvLMrIrrvcF1q17iIJqkkJh466lBs0aFJpxjRW6g90cF29%2F1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/siruchoice/products/11335082320</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -34522,7 +34510,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=xfEXWvnbgvnIDXi9ZUK7%2Fv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdWOtnijP6LWfckBdrIidRnR%2Ff9B0MUCKxR52R9Mt7tK7FkzES0wGQEm142bzU%2FSHGqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tkWOhQtCMfH5YPRfVKDAv0injJ0cbUk%2B7WkMZYYLCLnKi1eYscjgtdhV4FDznS96ycCs2h3Jodx2PwBoC3RZ4TPUyXJ3AH1YCGRRQL0o7SKXUNwtj8Qo5Kve4QWMBuU5L1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/12705107393</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -34572,7 +34560,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=gJm4o1KOgs7Ep3MWtoyKQ%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfU0WqjsuBNKrJGei2gfmO0D6B7zODKO73pcwVaSe7S%2FozQ%2BQ5GMAcu5%2BfBDmzGqzWqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tNjXcAKxGmRlmZoHSVRBhTfyMcGZS1Wzdh9oz1wlq8s2i1eYscjgtdhV4FDznS96y7UwC2b1t6wCuh5Q3Gu%2BLimUOnZXJ7umC%2BrlnezzJwyRcoojlSPXYdpJoerySzB931S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/sawpalcosanol/products/6333517167</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -34622,7 +34610,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=NvGdCWxWkP6ygsMg2ZIJDv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtf1zTAb3YoNEYKobFykn%2BabGy0E4axmcQprFaOfPGMJF3IaUDRr3Nsix9rQ%2B70nenuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tfZjX83qjYL4paDgVgSqKyjuQUOqPNTpLHMcG%2Fqamq3Oi1eYscjgtdhV4FDznS96yu%2FqWHh9LJcGlKEqizwabBXobvtWhmy95rbfen%2B9vRR2Z4N9ikDTEIoenBP3SEjJ71S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/healthyday/products/741820195</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -34672,7 +34660,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=9VduHQm3KgFpNkB3fjzuyv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtd17z%2FwF5DvCAvA9wpYdMIodURh6uk%2Fm4DHdmWTsUjtQu39CzNceJh%2F6OoGXR%2F%2BqVaqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tIYbaqGnGTOQofVUw7%2BpQ5gFKyuoMBTHu3bKeAW7y2dei1eYscjgtdhV4FDznS96ylgE5iftaUCo%2BhjGB5n0O80JqSpC3sUhwv%2FcKGFd%2FCqkAdDsXk%2B%2FepqKcLIKfAE9I1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/dswellife/products/13068265560</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -34722,7 +34710,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=7osTPt%2BgYLnXDnlGqQdILP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteGxsN1P8XG8XuWHMxjpKZM8ZI8SVVFf1%2FWpp40d8Cf2K2jCbmgt9ih44Ma%2BRORe82qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tgmi8d8LxA8HCTrTvFay0fmUvfiI10pSvzXVTvJhJs9ei1eYscjgtdhV4FDznS96yjIkowS1Wcud2oSfObstIPgbqWBoSOh66Esp4YxuuFYpIwwQvTYWWPNiji86UjYf31S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/june__market/products/12085385840</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -34756,72 +34744,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -34858,7 +34846,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=cTMvTnMlSbF3ySVLmI47Tf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdTBxzO63r6YjAx2hjpTwwYI8cSFyx5VUn9vQjGkbfJQvzuyO3j2mPwHQOY58BP%2B%2FuqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tZitTspPhgAxBcse2l2ZsaZlBGwijsf%2B5rISqkcbYMOii1eYscjgtdhV4FDznS96ynnGTXVHe43bp69kRdL0I1gZ7cX1VKSpUc8j0j0HUlguOVemK8%2BnC2%2FJN74JDXm1x1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/dr_phyto/products/8990669497</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -34908,7 +34896,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=%2F0ppaxkinoxEWRzkLvvHNP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtf7dasDTq%2FWro%2FAWS4rT5MKe5XRhJkn3z8M2VRAkZJNktnqJIsCIZaeb9%2FuLHNxjQKqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1ta9P6P7PnYDY1cE0weP4WVKc%2Bux0n6X598sz7rhrgCHGi1eYscjgtdhV4FDznS96ycjC5oIDIwgViSFP%2FgTsLMXbm8W0%2BZUTSYMBEoa4WJzjQ2EyKfLZW21b309epTR3o1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/happyenzyme/products/8950954958</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -34958,7 +34946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=pTFLixqXw3CcPqF5str02v%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcYUdUkVRVvuIK%2FT%2Bzjs27CZ4CQuHqbTCMAMG4micGnkb6pACEEumf0clSdWw3ajt2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tYQDQfuL4HfP6aOZvh9iKE49qPPQFzmClFv1iGXlWT5Ci1eYscjgtdhV4FDznS96y0ZUnjyV6weZcAh9mgEXnpHFsJ6ZX5r86s%2FZokRkYKgWl1Qk79Xdno7mM3NUlbzJm1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/nutright/products/9914864124</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -35008,7 +34996,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=VhdgB1uysrMi6IGhihAAT%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteSFd%2BGwTagFvhmrmQctMi1Otn7VzqNOG0KEY32G4aRE3aD9SOgGwxspusVZ3bvZd%2BqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t3rgKE3%2F5fFj%2BN%2F7j6XuqPc5T%2Bjm69IbTkze5U8mTD4mi1eYscjgtdhV4FDznS96yPkXj5kk%2FVnFpg35Qv3k7k%2BRTexKsYpYoU52aw3FUO5n%2Berp1pFKGJKosbXK644I21S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/lactiv/products/11146379810</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -35058,7 +35046,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Q180X7WKsZW9WdzW3jwDBf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdFJGqcAqUfUQA2QKyT3QZ18HoBtwr52ZNCHw%2FbmbWlC%2FJOtOCUZ2397efspbG300OqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1thCLVK6mYYCUxzeSdWBQnIQ1ws2mLNaKn9qKT842d1QWi1eYscjgtdhV4FDznS96y%2BAqzWtHIdLe9H2WAATlTU%2Fxl3ATONJ5m%2FFABcVus5YHN9K6fbNkQlQKXDa2AMSVf1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/grainon/products/9327855716</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -35108,7 +35096,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=AbhdXlpqQj5daDqearP%2Fw%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfKGCckwRl%2FWWojTlruTURcLbj3vhRyYGzf31V2vHrMA%2BxVLuM8rxiquxYumHLQB7iqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tEaBgChomQNLxi9spApQP8A2vpI5atdRoPn%2FCXlIArm2i1eYscjgtdhV4FDznS96yk7O4Yhlbv3z0Yq7NjNbyyuR4JT1rr4lAqpVWhZoznl%2Fpj085stKp0Z0pXUgO0n%2BN1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/5184170043</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -35158,7 +35146,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=L16v73nnLnIu2OGy8b%2BYDv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcQ1cFjdiTP%2FpUSIiuukqGNmdVJLClA%2B6Y8dfNalEeADrcQ5YcQJpi7aAD9LkgE3X2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tZuXo5yPzU3T0rnxPfTVBuV7lRjo2Kyfub793SUOocqyi1eYscjgtdhV4FDznS96yeJERM%2Bz0A8XqvI8n5TvolUyoLZiPoO1lbTK9YX%2BheTf4z%2FNEW2ZZX5kp7%2BTrG6Mi1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/dswellife/products/9718326638</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -35208,7 +35196,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=71IbaTRw0z0h1INBraPDPf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtewwLMhJ7VQcK8XDIzgt0Scgz0aCDeBLBX32aTkoap%2F6Ksn7ymxM7fgNXn7JC7omX2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tKgw%2BVYwtTbdjVxV7Rsf0O079N144iQ9CDoJTFVEomr6i1eYscjgtdhV4FDznS96yeVYgc6QkABSmr1WFe3JkIuNcOU1TRJ4%2BI%2Fp%2FRjoYb3zMJzq31WRQRT0PAsjDtZvN1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/rokitamerica/products/6043695503</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -35258,7 +35246,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=NhSLr5NNesTIHwAPO9dOTf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfExi9rGqDTh78DMvRRXjsFKfCh9jz2pob9BgSLnoRyitbl3iAIxRkK6kMCmGZQgZOqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1toULAO11o0m2g5mgEnm%2BWPOITSplGwlCwlf%2FCDo3Ie0ei1eYscjgtdhV4FDznS96ypCIoMKtTEeG418RZhm0wTA2iGAzaFYpIYeq6tjFYz2S8sQhXYHDuUT38C0KB45NR1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/wannabein/products/9319091551</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -35308,7 +35296,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=auJrl0ZmWffBfklzj4Nh5P%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfOe7Qrukq4y0v84%2FNcZbE7QSRnm%2BvBxeodYI6WkTDE80nvaro544pHRcQOu6fk2DyqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tE9OTKt0ON9Aw3MsNNK410OQ3HV2A8WSS4O6Ll6A2BUCi1eYscjgtdhV4FDznS96yCpclT2%2FAcN%2Bd%2FNk4l60u3w4qkr7u687hetUhiDZM%2FSkhoFjo5Iq2Wxl106Xh5pmb1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/ph365korea/products/4762660973</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -35358,7 +35346,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=6I7ZAoi3UvGRhsqOxFB%2FMP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfkyJeDZ6DnIlP3ECaALbc5ZgzoXaZ%2F%2BtJqbW19RVx5S%2F9S8dK5A2PqGHIWpUqfaHWqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tPhydzqR%2F8%2BYKLIyhREMbrwc9%2FSjtyyF3xjcdlCKkZBSi1eYscjgtdhV4FDznS96yfYnjcBE7VxkGpD1D3rJ%2FfkXU1QgncDicNIhhh0Y0cJqda2qMwdnsQE7JhmItQc%2Fp1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/11243018665</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -35408,7 +35396,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=ZKnhXUFN1HulxfTAhycvJ%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfIhkH25RVVB1sYJBJkTZ9yTtLPTYQSsERrjyQYZ%2Bgk2YiwmCSlEKxXvrO3nYMYqP2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tGALQvgqm5UA1oUzntBSU5xTIRq8BpPl3sZmzzDoszWSi1eYscjgtdhV4FDznS96y5DQ2%2F2nFPIMhNO5%2FHRcQEegnKQAmh8HNPgCKlgd%2B6%2FYpp0lM8kFimlcOSofg%2BzXH1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/ssgbio/products/10829472054</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -35458,7 +35446,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=uBUlYrhCbYrJir6aBY%2B%2BLP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdEgkKus2LFOrK9MKlRpU6tjb00a5bRRxZLbWipp5AK3XXF6xBf1W3PeEhXzrkP5WSqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tosQEsomAMvVTTSOT8jdaX3cPDpUd%2FqWuFXn07K938iKi1eYscjgtdhV4FDznS96ypw%2BCxR0O1veW488AQl%2BhDCVm3VS0ElWZJRZTC3yY4PZgiFybDcvjlIzHBygTVwS11S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/bluezon/products/11122300857</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -35508,7 +35496,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=hr0mpWlwKpkhSKOOh61xDf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfVjhUrYQf51UsrvQvYXPiLBR73HCH%2B0QHHXsvfvR2HFkcZEsjqIauAW90I1Q3tPRyqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1t%2BCdBx%2FBk8rAyoLnzIneB5A6mqjQXEADQQYU%2B2JGCR%2BKi1eYscjgtdhV4FDznS96yj72GSvwLOglr0hVSfIa5AyfIreOEu4ZcJjhL1KlrciP8czD2t04L9HzXMHPlxPqx1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/11038594172</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -35558,7 +35546,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=YkvoetK0F%2BEcEtgsNT2jXP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcUVXSntNpmsfSGW%2BgqKXQjq02%2F0Z3tX9R6NvhSsuilf4IxYFqRSAHwcrM48Wy6YZWqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tSCSzkLHnbmKcbhGxbKF5JZvYwBaYmINM9Sehr4rvBZai1eYscjgtdhV4FDznS96ywTbjTLuaQ2kbiCcFi%2Fl7mhXGsQtOVf1XaVnXboQXZaGG%2FLEoOuK0IvogzLL%2Fa40r1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/yuhanotc/products/8473114714</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -35608,7 +35596,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=2yoR5edG2%2FupWFqUEpSlgP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfYyexy8uSHZGOdbc9l6JeEip5fpmMyrMIyT%2BHTJA7zDlnibvIqpmKbWwfVFVuP75KqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tHVU76eWcFWbiU61yzNzMO56YgjQikkL3fnHrXcnCNvii1eYscjgtdhV4FDznS96yXGk9DAyf12XIYaNsckJywh60D4kCT4wHEC%2BKP1ueRtJ0n66ljVzSEXN%2Fci2ZxMV61S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/bodynalthin/products/12968163569</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -35658,7 +35646,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=VGmeV7gffj1EYMZd%2ByPN6v%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhte1MR42c%2BQnO7oKI7ZXXRDkc5bSSdBwfCC%2FZ5QOQP%2BUCxdxIwYiMvADD5m4lWeiEJKqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tBnWd%2BHUJkt1rf5rQyKEjXy2ulVr65t1B6Y86AoQfp2Oi1eYscjgtdhV4FDznS96y4ysNnL1fiKedtUOEz1xA%2FUmqfJS3y%2BJWsVhdLTJTKpu%2Fl9VVf7PUqPcKJd3xOqVF1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/gnm/products/2386338454</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -35708,7 +35696,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=4%2F7IOlpP8NUQngYHvKT9tf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtfs37M9vs7qfaALgKv2s1%2FZi8mD72Qb%2BLhett2jXJefVHRCIVaJRuYVuLPzmXxTz5eqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tyG9nB1RPizZQPmHoLyAlxo%2BfhIypzz%2BxxTkCAcTAPOei1eYscjgtdhV4FDznS96yPvydxPJ0ODlb6TWXV%2FXa%2Bj2PmMYzbhgCgssaZc5sfoO1LVv%2B33gpJEWxqQrO3CuH1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/cj_wellcare/products/12154127416</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -35758,7 +35746,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=WIjifzh7RGjEgePnCQkT3%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtc5FYbmEs3pbUO4ZPNSFRKtO5UeATQLJn%2FXjM4%2Fohbl%2Fx7GRwL2DImMw00y3LT%2BO4yqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tEqPqJRTUGDgfzQg%2BSOGWCaoHfh5T3PDu44CN3rgEHb2i1eYscjgtdhV4FDznS96yTpeTMP6qW5VBJPZCvTrVmhP1q4PvC%2F2dGHCVYFpplDMTyY0VAgjxRdFgfu3g0XLe1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/nutrimoremall/products/7285790085</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -35808,7 +35796,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=blFaqAarbrIfbzzfEMwQTf%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhte7Y1Lgt2%2FlwibEQtGoRlIKUHb3MoZC5e2gK5hJ3N2XrsaF6nPA%2Fzr4EIsRaC80TYeqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tF%2BDcmQWdR6tHd52aCOxHkj2vrniGv1QeDwHhTmIE8zii1eYscjgtdhV4FDznS96yCpjVtqrl%2Fl2gBCVvnVgWUyNAVcnfzPuCJOlRPbqb514KEhkqViZFP30FkLjrZXO71S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/dr_lean/products/12913969396</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -35858,7 +35846,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=cwsH5tMO1yZ7FeBLEQPdoP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdgePrn9U1by%2FoSfG0tRGFjSUjFQ37e9QSKpamCVUHlnXtt2JZSnBH5F2N2FbQ%2BEcGqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tWSFHLuG7H5XyN0qAgM6Br%2BVwKF8Y7hvHzMVIlmQm%2BAii1eYscjgtdhV4FDznS96yfMA6l59Cdv%2BdJvbraqXfQ76xBZzr2UpRvbMBaevCfHluxYgD%2F0mG0yJmKaKZCkhK1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/lactiv/products/10718647050</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -35908,7 +35896,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=Zr%2FgYltYVwKkWsdRVFu86f%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhteIV10AC1z0G7IHA9kvzmmkFSXgPbJYlUPH2ArGR1cV02P%2BAkGpE%2FKHfeeNXcrzzuOqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tQLA00LoirW4iDgdGAw5yV5%2Fu0cGzMu%2Buac15p3xI1Eei1eYscjgtdhV4FDznS96y%2F%2BwswNI%2FnIBpWQafYkhKd%2B%2F%2Fwv%2FfKK9A%2BIonjQzlLM95EXKMkLNxfEmA%2Bhh7yfNy1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/webiom/products/11311792713</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -35958,7 +35946,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=KzrDScozlk3nAeiatCgDNP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhte9pgZ6s396xiJjkBOYCOra0FEPYReuXB8Y4KjPoY6xfGTuhqtlqmOcwDLTLGFsRLSqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1taOuEIj8FAfUXGUhl%2BPRfPOVIF7Noqa4sewQXhDr9Yf2i1eYscjgtdhV4FDznS96y39kTYDMwRjFjgpntUTn0vOwLr0%2BYGTyBoMBBPZKaqJYL95jo2mrm5K%2Fpb8OK60GB1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/patternkorea/products/12683992303</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -36008,7 +35996,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=M0s5dvh%2FJIZnYvf4VvIGO%2F%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtdMQffsmxGxVeFGRscBeP5CSK8IxvJPFvPQQ9yrcYyWBkO5kmBAGpRhSarQFXryrf%2BqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tdUI8ssWw3pqSw5FSRtZm3W0jokvaCbQRpq0qfm3bdUKi1eYscjgtdhV4FDznS96y9TB5qXb3OJTIItpnJf3pZnlhrm2WztAlWygJzrIqu2%2FAqgWKiiwnkGQN7cVBf2H51S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/koreaeundanhc/products/5410453538</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -36058,7 +36046,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=IkryhDURvwsE7V5vhPTyGv%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtf3tCGo%2B4LfTPwPaJwzGbi1%2B%2Bgz60p4JeveB4p5P90iLCv14qWBr2IW%2Fc9nxf9UPHeqNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tkR7sv3sN%2FDIThYvI%2B4Uoa%2BqvfpeDYPlyuUzwBJVYHhCi1eYscjgtdhV4FDznS96yWD129qqOXSbb4TKhiZbNZ3lh1dCoorWmuu9uNFG0bou2kvP%2BaMc1ZgJprTfjP7S51S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/withvinestore/products/9806724450</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -36108,7 +36096,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://adcr.shopping.naver.com/adclk.nhn?x=454wmrNZ30m8HAx2NPTyHP%2F%2F%2Fw%3D%3Dsmd8zBqMJQLjellaiFGSaxelHjPrOWjZx0d%2BfAbCirfJS0MlE9Zhp0ZdexlLGrR6%2FG7G5RJJUxF5j92Eo1iXTsoZdhCE9OcMVyJIwnPrYIuSE%2Fj5XTbEpO%2Ff%2BCOlfySNolxSW4jN8tjTE9p7Dw21Cgajuk1jLAABprluavCCwhtcTAjRsucOAxLKmTh1OUwq65e2RKpV7aoRl7z9CC9uBi%2BaXy5vwSlJzQAGJ67c3dT2qNJLHDvkAeNagZxwY00sHzZU6tOWYvXDtfe%2FKTLZmvOTrhNA2Y9DYlJn9x7c0rDaIREIpNVhYg0zNI7RA9puuQ2GKTll6cJfm2B0m02yaeq06zyyIjhpDGYHRny7VExN7Fl3DIAO81ecxdkP8Nr1tsKNhgjxT99TO7GQGnvP6OpijQzLty10N%2Fq1eAfuLaJ%2Bi1eYscjgtdhV4FDznS96yQX1nFEHX9g4eb%2FrIMRxBqwcoOp8a11s8i018yZk3cVX%2Bd%2BY5aReYzWIX7MD7GGf%2F1S2%2F8DDBJozM%2BIUdZXMaqZynIXKi7mxrfmrVNAqOnBY89HjmzpGDa%2Be1vEcYCZbBUWnEuM9LolkgCDalFY4sk0HWeGx17iNtpkho8zQdCxg%3D</t>
+          <t>https://smartstore.naver.com/just_follow/products/11574019686</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -36142,72 +36130,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -36704,72 +36692,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -37290,72 +37278,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>review_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>star_diff</t>
         </is>
@@ -37576,52 +37564,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
@@ -38038,52 +38026,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
@@ -38584,52 +38572,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>period_ym</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>price_diff</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>rank_diff</t>
         </is>
